--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichaelBurke\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F57A54A-3313-4E07-AEC7-E0A9CF12BED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD515704-9AA8-4503-ADC2-8F1BE24C54D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -1037,10 +1037,10 @@
         <v>47665</v>
       </c>
       <c r="B56" s="2">
-        <v>64.405000000000001</v>
+        <v>64.025000000000006</v>
       </c>
       <c r="C56" s="2">
-        <v>3.4430000000000001</v>
+        <v>3.4279999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1365,7 +1365,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A56:B85 A2:A55" numberStoredAsText="1"/>
+    <ignoredError sqref="A57:B85 A2:A55 A56" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichaelBurke\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD515704-9AA8-4503-ADC2-8F1BE24C54D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C7C40C-1D33-4599-841E-11C9987AA209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19400" yWindow="14380" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
